--- a/data/filtered/china_war.xlsx
+++ b/data/filtered/china_war.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I329"/>
+  <dimension ref="A1:N329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,31 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>是否春节档</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>是否国庆档</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>是否五一档</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>是否暑期档</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>是否普通周末</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>详情链接</t>
         </is>
       </c>
@@ -498,7 +523,22 @@
           <t>1985-11-07</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1422283/</t>
         </is>
@@ -539,7 +579,22 @@
           <t>1991</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1424552/</t>
         </is>
@@ -580,7 +635,22 @@
           <t>1991-08-01</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1424551/</t>
         </is>
@@ -621,7 +691,22 @@
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10450409/</t>
         </is>
@@ -662,7 +747,22 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6393127/</t>
         </is>
@@ -703,7 +803,22 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1307729/</t>
         </is>
@@ -744,7 +859,22 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36809864/</t>
         </is>
@@ -785,7 +915,22 @@
           <t>2012-05-10</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3993559/</t>
         </is>
@@ -826,7 +971,22 @@
           <t>1991</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1980790/</t>
         </is>
@@ -867,7 +1027,22 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2132220/</t>
         </is>
@@ -908,7 +1083,22 @@
           <t>2001-04-11</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308078/</t>
         </is>
@@ -949,7 +1139,22 @@
           <t>2009-09-29</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3734112/</t>
         </is>
@@ -990,7 +1195,22 @@
           <t>2020-08-07</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30252495/</t>
         </is>
@@ -1031,7 +1251,22 @@
           <t>1988-10-10</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1306505/</t>
         </is>
@@ -1072,7 +1307,22 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1307201/</t>
         </is>
@@ -1113,7 +1363,22 @@
           <t>1965</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3033864/</t>
         </is>
@@ -1154,7 +1419,22 @@
           <t>2011-12-15</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3649049/</t>
         </is>
@@ -1195,7 +1475,22 @@
           <t>2016-11-11</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25983044/</t>
         </is>
@@ -1236,7 +1531,22 @@
           <t>2018-02-16</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26861685/</t>
         </is>
@@ -1277,7 +1587,22 @@
           <t>2012-11-29</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6011805/</t>
         </is>
@@ -1318,7 +1643,22 @@
           <t>2007-12-20</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1907464/</t>
         </is>
@@ -1359,7 +1699,22 @@
           <t>1988-12-01</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1401124/</t>
         </is>
@@ -1400,7 +1755,22 @@
           <t>1956-12-01</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1433701/</t>
         </is>
@@ -1441,7 +1811,22 @@
           <t>1983</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1305103/</t>
         </is>
@@ -1482,7 +1867,22 @@
           <t>1987-10-23</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308607/</t>
         </is>
@@ -1523,7 +1923,22 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1466273/</t>
         </is>
@@ -1564,7 +1979,22 @@
           <t>1990</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1464535/</t>
         </is>
@@ -1605,7 +2035,22 @@
           <t>1990-11-23</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1296334/</t>
         </is>
@@ -1646,7 +2091,22 @@
           <t>2014-11-21</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/23331914/</t>
         </is>
@@ -1687,7 +2147,22 @@
           <t>1963</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1464540/</t>
         </is>
@@ -1728,7 +2203,22 @@
           <t>2016-03-11</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25757187/</t>
         </is>
@@ -1769,7 +2259,22 @@
           <t>2007-12-12</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1947089/</t>
         </is>
@@ -1810,7 +2315,22 @@
           <t>1993-05-24</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1302941/</t>
         </is>
@@ -1851,7 +2371,22 @@
           <t>1996-04-25</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1305182/</t>
         </is>
@@ -1892,7 +2427,22 @@
           <t>1963</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1461964/</t>
         </is>
@@ -1933,7 +2483,22 @@
           <t>1964</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1438091/</t>
         </is>
@@ -1974,7 +2539,22 @@
           <t>2020-07-10</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26871906/</t>
         </is>
@@ -2015,7 +2595,22 @@
           <t>2022-10-01</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35358429/</t>
         </is>
@@ -2056,7 +2651,22 @@
           <t>2023-07-20</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10604086/</t>
         </is>
@@ -2097,7 +2707,22 @@
           <t>2017-12-15</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26862829/</t>
         </is>
@@ -2138,7 +2763,22 @@
           <t>2014-12-23</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10807909/</t>
         </is>
@@ -2179,7 +2819,22 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35215390/</t>
         </is>
@@ -2220,7 +2875,22 @@
           <t>1963-02-02</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1422286/</t>
         </is>
@@ -2261,7 +2931,22 @@
           <t>1989-09-21</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3147497/</t>
         </is>
@@ -2302,7 +2987,22 @@
           <t>1995-07-07</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1919098/</t>
         </is>
@@ -2343,7 +3043,22 @@
           <t>2009-04-22</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2294568/</t>
         </is>
@@ -2384,7 +3099,22 @@
           <t>1999-09-29</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1298874/</t>
         </is>
@@ -2425,7 +3155,22 @@
           <t>2006-09-01</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1949812/</t>
         </is>
@@ -2466,7 +3211,22 @@
           <t>2020-08-21</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26754233/</t>
         </is>
@@ -2507,7 +3267,22 @@
           <t>2018-01-12</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6874741/</t>
         </is>
@@ -2548,7 +3323,22 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2364059/</t>
         </is>
@@ -2589,7 +3379,22 @@
           <t>2019-11-08</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26786669/</t>
         </is>
@@ -2630,7 +3435,22 @@
           <t>2009-04-29</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2294565/</t>
         </is>
@@ -2671,7 +3491,22 @@
           <t>1996-11-01</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1305034/</t>
         </is>
@@ -2712,7 +3547,22 @@
           <t>1989-10-20</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1293759/</t>
         </is>
@@ -2753,7 +3603,22 @@
           <t>1974-10-01</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1461985/</t>
         </is>
@@ -2794,7 +3659,22 @@
           <t>2021-09-30</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25845392/</t>
         </is>
@@ -2835,7 +3715,22 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1394968/</t>
         </is>
@@ -2876,7 +3771,22 @@
           <t>1956</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1434172/</t>
         </is>
@@ -2917,7 +3827,22 @@
           <t>1997-06-09</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1305366/</t>
         </is>
@@ -2958,7 +3883,22 @@
           <t>2001-05-04</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1306346/</t>
         </is>
@@ -2999,7 +3939,22 @@
           <t>1987-07-09</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1306396/</t>
         </is>
@@ -3040,7 +3995,22 @@
           <t>2022-09-30</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26654184/</t>
         </is>
@@ -3081,7 +4051,22 @@
           <t>2022-02-01</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35613853/</t>
         </is>
@@ -3122,7 +4107,22 @@
           <t>2017-09-22</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27063335/</t>
         </is>
@@ -3163,7 +4163,22 @@
           <t>1962</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1394315/</t>
         </is>
@@ -3204,7 +4219,22 @@
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35461578/</t>
         </is>
@@ -3245,7 +4275,22 @@
           <t>1990-07-28</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1307569/</t>
         </is>
@@ -3286,7 +4331,22 @@
           <t>2017-07-27</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26363254/</t>
         </is>
@@ -3327,7 +4387,22 @@
           <t>1979</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1309226/</t>
         </is>
@@ -3368,7 +4443,22 @@
           <t>1984-11-02</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1300553/</t>
         </is>
@@ -3409,7 +4499,22 @@
           <t>2010-08-19</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4825006/</t>
         </is>
@@ -3450,7 +4555,22 @@
           <t>1955</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1482709/</t>
         </is>
@@ -3491,7 +4611,22 @@
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36296619/</t>
         </is>
@@ -3532,7 +4667,22 @@
           <t>1955</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1452554/</t>
         </is>
@@ -3573,7 +4723,22 @@
           <t>1958</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1464618/</t>
         </is>
@@ -3614,7 +4779,22 @@
           <t>1954</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1461981/</t>
         </is>
@@ -3655,7 +4835,22 @@
           <t>1961</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1424630/</t>
         </is>
@@ -3696,7 +4891,22 @@
           <t>2015-04-02</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24753810/</t>
         </is>
@@ -3737,7 +4947,22 @@
           <t>1960</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1916282/</t>
         </is>
@@ -3778,7 +5003,22 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1</v>
+      </c>
+      <c r="N82" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26671336/</t>
         </is>
@@ -3819,7 +5059,22 @@
           <t>1935-01-01</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1307015/</t>
         </is>
@@ -3860,7 +5115,22 @@
           <t>1996</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2262160/</t>
         </is>
@@ -3901,7 +5171,22 @@
           <t>1952</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1463390/</t>
         </is>
@@ -3942,7 +5227,22 @@
           <t>2023-09-28</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35496350/</t>
         </is>
@@ -3983,7 +5283,22 @@
           <t>1959</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308306/</t>
         </is>
@@ -4024,7 +5339,22 @@
           <t>1998-07-22</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1298207/</t>
         </is>
@@ -4065,7 +5395,22 @@
           <t>2006-12-01</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1949811/</t>
         </is>
@@ -4106,7 +5451,22 @@
           <t>2019-08-01</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30261964/</t>
         </is>
@@ -4147,7 +5507,22 @@
           <t>1970-10-01</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1438274/</t>
         </is>
@@ -4188,7 +5563,22 @@
           <t>1954</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1482707/</t>
         </is>
@@ -4229,7 +5619,22 @@
           <t>1996</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2262170/</t>
         </is>
@@ -4270,7 +5675,22 @@
           <t>1999</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3444043/</t>
         </is>
@@ -4311,7 +5731,22 @@
           <t>2012-04-24</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6080775/</t>
         </is>
@@ -4352,7 +5787,22 @@
           <t>1997</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3403157/</t>
         </is>
@@ -4393,7 +5843,22 @@
           <t>2017-07-01</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26425072/</t>
         </is>
@@ -4434,7 +5899,22 @@
           <t>1933</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1298619/</t>
         </is>
@@ -4475,7 +5955,22 @@
           <t>1998</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2262149/</t>
         </is>
@@ -4516,7 +6011,22 @@
           <t>2017-03-08</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26990713/</t>
         </is>
@@ -4557,7 +6067,22 @@
           <t>1994-01-11</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1482698/</t>
         </is>
@@ -4598,7 +6123,22 @@
           <t>1996</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2130014/</t>
         </is>
@@ -4639,7 +6179,22 @@
           <t>1995-09-14</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1297607/</t>
         </is>
@@ -4680,7 +6235,22 @@
           <t>2024-09-30</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36296618/</t>
         </is>
@@ -4721,7 +6291,22 @@
           <t>1983</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1304771/</t>
         </is>
@@ -4762,7 +6347,22 @@
           <t>1994-06-09</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1305143/</t>
         </is>
@@ -4803,7 +6403,22 @@
           <t>2002-11-21</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1306929/</t>
         </is>
@@ -4844,7 +6459,22 @@
           <t>1958</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1493578/</t>
         </is>
@@ -4885,7 +6515,22 @@
           <t>2003-05-22</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1303217/</t>
         </is>
@@ -4926,7 +6571,22 @@
           <t>1991</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1307496/</t>
         </is>
@@ -4967,7 +6627,22 @@
           <t>1984-08-02</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>1</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1298199/</t>
         </is>
@@ -5008,7 +6683,22 @@
           <t>2005-08-15</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>1</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2006172/</t>
         </is>
@@ -5049,7 +6739,22 @@
           <t>2018-10-26</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6538807/</t>
         </is>
@@ -5090,7 +6795,22 @@
           <t>2015-08-21</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26382797/</t>
         </is>
@@ -5131,7 +6851,22 @@
           <t>2011-09-23</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4896305/</t>
         </is>
@@ -5172,7 +6907,22 @@
           <t>2012-08-04</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>1</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25739362/</t>
         </is>
@@ -5213,7 +6963,22 @@
           <t>2008-04-03</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1923474/</t>
         </is>
@@ -5254,7 +7019,22 @@
           <t>1963</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1483955/</t>
         </is>
@@ -5295,7 +7075,22 @@
           <t>1996</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3403158/</t>
         </is>
@@ -5336,7 +7131,22 @@
           <t>1961</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1498716/</t>
         </is>
@@ -5377,7 +7187,22 @@
           <t>2009-09-08</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3778246/</t>
         </is>
@@ -5418,7 +7243,22 @@
           <t>2008-07-10</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>1</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1465829/</t>
         </is>
@@ -5459,7 +7299,22 @@
           <t>2009-01-08</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3291930/</t>
         </is>
@@ -5500,7 +7355,22 @@
           <t>1977-08-02</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1876476/</t>
         </is>
@@ -5541,7 +7411,22 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1437842/</t>
         </is>
@@ -5582,7 +7467,22 @@
           <t>2020-10-23</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35155748/</t>
         </is>
@@ -5623,7 +7523,22 @@
           <t>1991-03-28</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1419925/</t>
         </is>
@@ -5664,7 +7579,22 @@
           <t>2001-01-01</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1299864/</t>
         </is>
@@ -5705,7 +7635,22 @@
           <t>2010-11-05</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5045804/</t>
         </is>
@@ -5746,7 +7691,22 @@
           <t>2001-09-07</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1296520/</t>
         </is>
@@ -5787,7 +7747,22 @@
           <t>2013-04-04</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5996799/</t>
         </is>
@@ -5828,7 +7803,22 @@
           <t>2025-01-29</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
+      <c r="I132" t="n">
+        <v>1</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35295960/</t>
         </is>
@@ -5869,7 +7859,22 @@
           <t>2006-11-23</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1455979/</t>
         </is>
@@ -5910,7 +7915,22 @@
           <t>1953</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1822209/</t>
         </is>
@@ -5951,7 +7971,22 @@
           <t>1993-09-08</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1303227/</t>
         </is>
@@ -5992,7 +8027,22 @@
           <t>1987-12-03</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1915671/</t>
         </is>
@@ -6033,7 +8083,22 @@
           <t>2017-08-04</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>1</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26873799/</t>
         </is>
@@ -6074,7 +8139,22 @@
           <t>2023-09-28</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>1</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35775756/</t>
         </is>
@@ -6115,7 +8195,22 @@
           <t>1988-02-16</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1305595/</t>
         </is>
@@ -6156,7 +8251,22 @@
           <t>1994-06-10</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5290705/</t>
         </is>
@@ -6197,7 +8307,22 @@
           <t>2006-04-28</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>1</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1875311/</t>
         </is>
@@ -6238,7 +8363,22 @@
           <t>1951</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3008469/</t>
         </is>
@@ -6279,7 +8419,22 @@
           <t>2015-02-19</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
+      <c r="I143" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25823833/</t>
         </is>
@@ -6320,7 +8475,22 @@
           <t>2014-12-02</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3078390/</t>
         </is>
@@ -6361,7 +8531,22 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1830194/</t>
         </is>
@@ -6398,7 +8583,22 @@
           <t>2015-08-31</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26755033/</t>
         </is>
@@ -6439,7 +8639,22 @@
           <t>1989-12-21</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308229/</t>
         </is>
@@ -6480,7 +8695,22 @@
           <t>2017-05-27</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>1</v>
+      </c>
+      <c r="N148" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26385746/</t>
         </is>
@@ -6521,7 +8751,22 @@
           <t>2007-11-30</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2255992/</t>
         </is>
@@ -6562,7 +8807,22 @@
           <t>1963-05-01</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2033873/</t>
         </is>
@@ -6603,7 +8863,22 @@
           <t>1995-09-28</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2142197/</t>
         </is>
@@ -6644,7 +8919,22 @@
           <t>1979</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1302573/</t>
         </is>
@@ -6685,7 +8975,22 @@
           <t>2011-07-22</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6736369/</t>
         </is>
@@ -6726,7 +9031,22 @@
           <t>2008-06-22</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>1</v>
+      </c>
+      <c r="N154" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3239703/</t>
         </is>
@@ -6767,7 +9087,22 @@
           <t>2005-09-09</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1418407/</t>
         </is>
@@ -6808,7 +9143,22 @@
           <t>2025-01-29</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
+      <c r="I156" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30181250/</t>
         </is>
@@ -6849,7 +9199,22 @@
           <t>1960</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2138486/</t>
         </is>
@@ -6890,7 +9255,22 @@
           <t>2021-11-19</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35205446/</t>
         </is>
@@ -6931,7 +9311,22 @@
           <t>1996</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2340961/</t>
         </is>
@@ -6972,7 +9367,22 @@
           <t>1996</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1864542/</t>
         </is>
@@ -7013,7 +9423,22 @@
           <t>1965</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2274946/</t>
         </is>
@@ -7054,7 +9479,22 @@
           <t>1994-12-29</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1786332/</t>
         </is>
@@ -7095,7 +9535,22 @@
           <t>2024-06-18</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36466154/</t>
         </is>
@@ -7136,7 +9591,22 @@
           <t>2023-08-01</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36399580/</t>
         </is>
@@ -7177,7 +9647,22 @@
           <t>2021-04-02</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35231379/</t>
         </is>
@@ -7218,7 +9703,22 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1304408/</t>
         </is>
@@ -7259,7 +9759,22 @@
           <t>2004</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1872853/</t>
         </is>
@@ -7300,7 +9815,22 @@
           <t>1955</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2136122/</t>
         </is>
@@ -7341,7 +9871,22 @@
           <t>2017-11-10</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25865831/</t>
         </is>
@@ -7382,7 +9927,22 @@
           <t>1999-10-07</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1868115/</t>
         </is>
@@ -7423,7 +9983,22 @@
           <t>1991-03-28</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1296062/</t>
         </is>
@@ -7464,7 +10039,22 @@
           <t>2008-04-03</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1947091/</t>
         </is>
@@ -7505,7 +10095,22 @@
           <t>2012-07-06</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6080772/</t>
         </is>
@@ -7546,7 +10151,22 @@
           <t>1986-04-24</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4189670/</t>
         </is>
@@ -7587,7 +10207,22 @@
           <t>2014-09-19</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr">
+      <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25789352/</t>
         </is>
@@ -7628,7 +10263,22 @@
           <t>1988</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2282382/</t>
         </is>
@@ -7669,7 +10319,22 @@
           <t>1981</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1472247/</t>
         </is>
@@ -7710,7 +10375,22 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36894397/</t>
         </is>
@@ -7751,7 +10431,22 @@
           <t>1965-03-19</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1800766/</t>
         </is>
@@ -7792,7 +10487,22 @@
           <t>2006</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3113759/</t>
         </is>
@@ -7833,7 +10543,22 @@
           <t>1958</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1785628/</t>
         </is>
@@ -7874,7 +10599,22 @@
           <t>2011-12-02</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4328442/</t>
         </is>
@@ -7915,7 +10655,22 @@
           <t>1987</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr">
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2006991/</t>
         </is>
@@ -7956,7 +10711,22 @@
           <t>2022-09-24</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" t="n">
+        <v>0</v>
+      </c>
+      <c r="M184" t="n">
+        <v>1</v>
+      </c>
+      <c r="N184" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36097627/</t>
         </is>
@@ -7997,7 +10767,22 @@
           <t>2022-06-17</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr">
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="n">
+        <v>0</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0</v>
+      </c>
+      <c r="N185" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35474010/</t>
         </is>
@@ -8038,7 +10823,22 @@
           <t>1959</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr">
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1305227/</t>
         </is>
@@ -8079,7 +10879,22 @@
           <t>1964-07-29</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr">
+      <c r="I187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="n">
+        <v>1</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1772424/</t>
         </is>
@@ -8120,7 +10935,22 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr">
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/33429617/</t>
         </is>
@@ -8161,7 +10991,22 @@
           <t>2016-10-28</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr">
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="n">
+        <v>0</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26581128/</t>
         </is>
@@ -8202,7 +11047,22 @@
           <t>2012-04-23</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr">
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10508901/</t>
         </is>
@@ -8243,7 +11103,22 @@
           <t>1959</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr">
+      <c r="I191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2346533/</t>
         </is>
@@ -8284,7 +11159,22 @@
           <t>2003-12-23</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr">
+      <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3040614/</t>
         </is>
@@ -8325,7 +11215,22 @@
           <t>2011-03-12</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>1</v>
+      </c>
+      <c r="N193" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5343383/</t>
         </is>
@@ -8366,7 +11271,22 @@
           <t>1932-11-29</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11625164/</t>
         </is>
@@ -8407,7 +11327,22 @@
           <t>1974-07-19</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" t="n">
+        <v>1</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1918131/</t>
         </is>
@@ -8448,7 +11383,22 @@
           <t>2024-11-29</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr">
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36198699/</t>
         </is>
@@ -8489,7 +11439,22 @@
           <t>1976</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr">
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3324365/</t>
         </is>
@@ -8530,7 +11495,22 @@
           <t>2017-06-30</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr">
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26916202/</t>
         </is>
@@ -8571,7 +11551,22 @@
           <t>1989-01-18</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr">
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2035116/</t>
         </is>
@@ -8612,7 +11607,22 @@
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" t="n">
+        <v>1</v>
+      </c>
+      <c r="M200" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35231416/</t>
         </is>
@@ -8653,7 +11663,22 @@
           <t>2007-09-21</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2270516/</t>
         </is>
@@ -8694,7 +11719,22 @@
           <t>1976-05-28</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr">
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1304470/</t>
         </is>
@@ -8735,7 +11775,22 @@
           <t>1974-07-01</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2275036/</t>
         </is>
@@ -8776,7 +11831,22 @@
           <t>1965-10-22</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr">
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="n">
+        <v>0</v>
+      </c>
+      <c r="M204" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1307711/</t>
         </is>
@@ -8817,7 +11887,22 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" t="n">
+        <v>0</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0</v>
+      </c>
+      <c r="M205" t="n">
+        <v>0</v>
+      </c>
+      <c r="N205" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1834694/</t>
         </is>
@@ -8858,7 +11943,22 @@
           <t>1965</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" t="n">
+        <v>0</v>
+      </c>
+      <c r="M206" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1821518/</t>
         </is>
@@ -8899,7 +11999,22 @@
           <t>2013-03-22</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/21357362/</t>
         </is>
@@ -8940,7 +12055,22 @@
           <t>2007-08-24</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
+        <v>1</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2214084/</t>
         </is>
@@ -8981,7 +12111,22 @@
           <t>1976-04-16</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1302821/</t>
         </is>
@@ -9022,7 +12167,22 @@
           <t>1950</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr">
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" t="n">
+        <v>0</v>
+      </c>
+      <c r="N210" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1968505/</t>
         </is>
@@ -9063,7 +12223,22 @@
           <t>1987</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2007003/</t>
         </is>
@@ -9104,7 +12279,22 @@
           <t>2014-07-09</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr">
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10583840/</t>
         </is>
@@ -9145,7 +12335,22 @@
           <t>2016-09-15</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr">
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25945350/</t>
         </is>
@@ -9186,7 +12391,22 @@
           <t>2001</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr">
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1477865/</t>
         </is>
@@ -9227,7 +12447,22 @@
           <t>2013-05-01</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr">
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>1</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24522669/</t>
         </is>
@@ -9268,7 +12503,22 @@
           <t>1982</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr">
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2262174/</t>
         </is>
@@ -9309,7 +12559,22 @@
           <t>1987</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2256036/</t>
         </is>
@@ -9350,7 +12615,22 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2029655/</t>
         </is>
@@ -9391,7 +12671,22 @@
           <t>1993-05-01</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr">
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" t="n">
+        <v>1</v>
+      </c>
+      <c r="N219" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1302699/</t>
         </is>
@@ -9432,7 +12727,22 @@
           <t>1979</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr">
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" t="n">
+        <v>0</v>
+      </c>
+      <c r="N220" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2020610/</t>
         </is>
@@ -9473,7 +12783,22 @@
           <t>2017-09-29</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr">
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>1</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0</v>
+      </c>
+      <c r="N221" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26753020/</t>
         </is>
@@ -9514,7 +12839,22 @@
           <t>1959</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr">
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1925024/</t>
         </is>
@@ -9555,7 +12895,22 @@
           <t>1959</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr">
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" t="n">
+        <v>0</v>
+      </c>
+      <c r="N223" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3113758/</t>
         </is>
@@ -9596,7 +12951,22 @@
           <t>1998</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr">
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1858095/</t>
         </is>
@@ -9637,7 +13007,22 @@
           <t>1964-06-18</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr">
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2033962/</t>
         </is>
@@ -9678,7 +13063,22 @@
           <t>2020-08-07</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr">
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>1</v>
+      </c>
+      <c r="M226" t="n">
+        <v>0</v>
+      </c>
+      <c r="N226" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35123973/</t>
         </is>
@@ -9719,7 +13119,22 @@
           <t>1959-09-25</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr">
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1298298/</t>
         </is>
@@ -9760,7 +13175,22 @@
           <t>2016-10-14</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr">
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0</v>
+      </c>
+      <c r="N228" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26822683/</t>
         </is>
@@ -9801,7 +13231,22 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr">
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0</v>
+      </c>
+      <c r="M229" t="n">
+        <v>0</v>
+      </c>
+      <c r="N229" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2259755/</t>
         </is>
@@ -9842,7 +13287,22 @@
           <t>1992-08-28</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr">
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" t="n">
+        <v>1</v>
+      </c>
+      <c r="M230" t="n">
+        <v>0</v>
+      </c>
+      <c r="N230" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1472771/</t>
         </is>
@@ -9883,7 +13343,22 @@
           <t>1980</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr">
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0</v>
+      </c>
+      <c r="L231" t="n">
+        <v>0</v>
+      </c>
+      <c r="M231" t="n">
+        <v>0</v>
+      </c>
+      <c r="N231" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1472057/</t>
         </is>
@@ -9924,7 +13399,22 @@
           <t>1962</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr">
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" t="n">
+        <v>0</v>
+      </c>
+      <c r="L232" t="n">
+        <v>0</v>
+      </c>
+      <c r="M232" t="n">
+        <v>0</v>
+      </c>
+      <c r="N232" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1827612/</t>
         </is>
@@ -9965,7 +13455,22 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr">
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" t="n">
+        <v>0</v>
+      </c>
+      <c r="M233" t="n">
+        <v>0</v>
+      </c>
+      <c r="N233" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1937203/</t>
         </is>
@@ -10006,7 +13511,22 @@
           <t>1958</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr">
+      <c r="I234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L234" t="n">
+        <v>0</v>
+      </c>
+      <c r="M234" t="n">
+        <v>0</v>
+      </c>
+      <c r="N234" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2997305/</t>
         </is>
@@ -10047,7 +13567,22 @@
           <t>1994</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr">
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" t="n">
+        <v>0</v>
+      </c>
+      <c r="L235" t="n">
+        <v>0</v>
+      </c>
+      <c r="M235" t="n">
+        <v>0</v>
+      </c>
+      <c r="N235" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3240787/</t>
         </is>
@@ -10088,7 +13623,22 @@
           <t>2012-06-27</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr">
+      <c r="I236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0</v>
+      </c>
+      <c r="L236" t="n">
+        <v>0</v>
+      </c>
+      <c r="M236" t="n">
+        <v>0</v>
+      </c>
+      <c r="N236" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19969374/</t>
         </is>
@@ -10129,7 +13679,22 @@
           <t>1938</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr">
+      <c r="I237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" t="n">
+        <v>0</v>
+      </c>
+      <c r="L237" t="n">
+        <v>0</v>
+      </c>
+      <c r="M237" t="n">
+        <v>0</v>
+      </c>
+      <c r="N237" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1999622/</t>
         </is>
@@ -10170,7 +13735,22 @@
           <t>1976-01-31</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr">
+      <c r="I238" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="n">
+        <v>0</v>
+      </c>
+      <c r="L238" t="n">
+        <v>0</v>
+      </c>
+      <c r="M238" t="n">
+        <v>1</v>
+      </c>
+      <c r="N238" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3088432/</t>
         </is>
@@ -10211,7 +13791,22 @@
           <t>2006-10-18</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr">
+      <c r="I239" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" t="n">
+        <v>0</v>
+      </c>
+      <c r="L239" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" t="n">
+        <v>0</v>
+      </c>
+      <c r="N239" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2130006/</t>
         </is>
@@ -10252,7 +13847,22 @@
           <t>1960</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr">
+      <c r="I240" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>0</v>
+      </c>
+      <c r="L240" t="n">
+        <v>0</v>
+      </c>
+      <c r="M240" t="n">
+        <v>0</v>
+      </c>
+      <c r="N240" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2057374/</t>
         </is>
@@ -10293,7 +13903,22 @@
           <t>1988</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr">
+      <c r="I241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="n">
+        <v>0</v>
+      </c>
+      <c r="L241" t="n">
+        <v>0</v>
+      </c>
+      <c r="M241" t="n">
+        <v>0</v>
+      </c>
+      <c r="N241" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1422194/</t>
         </is>
@@ -10334,7 +13959,22 @@
           <t>2017-01-09</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr">
+      <c r="I242" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="n">
+        <v>0</v>
+      </c>
+      <c r="L242" t="n">
+        <v>0</v>
+      </c>
+      <c r="M242" t="n">
+        <v>0</v>
+      </c>
+      <c r="N242" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26891314/</t>
         </is>
@@ -10375,7 +14015,22 @@
           <t>2014-05-09</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr">
+      <c r="I243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="n">
+        <v>0</v>
+      </c>
+      <c r="L243" t="n">
+        <v>0</v>
+      </c>
+      <c r="M243" t="n">
+        <v>0</v>
+      </c>
+      <c r="N243" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19997896/</t>
         </is>
@@ -10416,7 +14071,22 @@
           <t>1981-08-27</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr">
+      <c r="I244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" t="n">
+        <v>0</v>
+      </c>
+      <c r="L244" t="n">
+        <v>1</v>
+      </c>
+      <c r="M244" t="n">
+        <v>0</v>
+      </c>
+      <c r="N244" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3435429/</t>
         </is>
@@ -10457,7 +14127,22 @@
           <t>1977-07-02</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr">
+      <c r="I245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" t="n">
+        <v>0</v>
+      </c>
+      <c r="L245" t="n">
+        <v>1</v>
+      </c>
+      <c r="M245" t="n">
+        <v>0</v>
+      </c>
+      <c r="N245" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1949145/</t>
         </is>
@@ -10498,7 +14183,22 @@
           <t>2019-08-08</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr">
+      <c r="I246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L246" t="n">
+        <v>1</v>
+      </c>
+      <c r="M246" t="n">
+        <v>0</v>
+      </c>
+      <c r="N246" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30468769/</t>
         </is>
@@ -10539,7 +14239,22 @@
           <t>1999-05-12</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr">
+      <c r="I247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J247" t="n">
+        <v>0</v>
+      </c>
+      <c r="K247" t="n">
+        <v>0</v>
+      </c>
+      <c r="L247" t="n">
+        <v>0</v>
+      </c>
+      <c r="M247" t="n">
+        <v>0</v>
+      </c>
+      <c r="N247" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1305153/</t>
         </is>
@@ -10580,7 +14295,22 @@
           <t>1973-12-21</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr">
+      <c r="I248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J248" t="n">
+        <v>0</v>
+      </c>
+      <c r="K248" t="n">
+        <v>0</v>
+      </c>
+      <c r="L248" t="n">
+        <v>0</v>
+      </c>
+      <c r="M248" t="n">
+        <v>0</v>
+      </c>
+      <c r="N248" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3797862/</t>
         </is>
@@ -10621,7 +14351,22 @@
           <t>2012-05-05</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr">
+      <c r="I249" t="n">
+        <v>0</v>
+      </c>
+      <c r="J249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K249" t="n">
+        <v>0</v>
+      </c>
+      <c r="L249" t="n">
+        <v>0</v>
+      </c>
+      <c r="M249" t="n">
+        <v>1</v>
+      </c>
+      <c r="N249" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10734527/</t>
         </is>
@@ -10662,7 +14407,22 @@
           <t>1962</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr">
+      <c r="I250" t="n">
+        <v>0</v>
+      </c>
+      <c r="J250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K250" t="n">
+        <v>0</v>
+      </c>
+      <c r="L250" t="n">
+        <v>0</v>
+      </c>
+      <c r="M250" t="n">
+        <v>0</v>
+      </c>
+      <c r="N250" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4914645/</t>
         </is>
@@ -10703,7 +14463,22 @@
           <t>1975-05-23</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr">
+      <c r="I251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J251" t="n">
+        <v>0</v>
+      </c>
+      <c r="K251" t="n">
+        <v>0</v>
+      </c>
+      <c r="L251" t="n">
+        <v>0</v>
+      </c>
+      <c r="M251" t="n">
+        <v>0</v>
+      </c>
+      <c r="N251" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1304385/</t>
         </is>
@@ -10744,7 +14519,22 @@
           <t>2020-11-06</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr">
+      <c r="I252" t="n">
+        <v>0</v>
+      </c>
+      <c r="J252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K252" t="n">
+        <v>0</v>
+      </c>
+      <c r="L252" t="n">
+        <v>0</v>
+      </c>
+      <c r="M252" t="n">
+        <v>0</v>
+      </c>
+      <c r="N252" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35225980/</t>
         </is>
@@ -10785,7 +14575,22 @@
           <t>2021-07-01</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr">
+      <c r="I253" t="n">
+        <v>0</v>
+      </c>
+      <c r="J253" t="n">
+        <v>0</v>
+      </c>
+      <c r="K253" t="n">
+        <v>0</v>
+      </c>
+      <c r="L253" t="n">
+        <v>1</v>
+      </c>
+      <c r="M253" t="n">
+        <v>0</v>
+      </c>
+      <c r="N253" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35295537/</t>
         </is>
@@ -10826,7 +14631,22 @@
           <t>2008-07-08</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr">
+      <c r="I254" t="n">
+        <v>0</v>
+      </c>
+      <c r="J254" t="n">
+        <v>0</v>
+      </c>
+      <c r="K254" t="n">
+        <v>0</v>
+      </c>
+      <c r="L254" t="n">
+        <v>1</v>
+      </c>
+      <c r="M254" t="n">
+        <v>0</v>
+      </c>
+      <c r="N254" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2972499/</t>
         </is>
@@ -10867,7 +14687,22 @@
           <t>1974-10-01</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr">
+      <c r="I255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J255" t="n">
+        <v>0</v>
+      </c>
+      <c r="K255" t="n">
+        <v>0</v>
+      </c>
+      <c r="L255" t="n">
+        <v>0</v>
+      </c>
+      <c r="M255" t="n">
+        <v>0</v>
+      </c>
+      <c r="N255" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20473376/</t>
         </is>
@@ -10908,7 +14743,22 @@
           <t>1961-12-08</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr">
+      <c r="I256" t="n">
+        <v>0</v>
+      </c>
+      <c r="J256" t="n">
+        <v>0</v>
+      </c>
+      <c r="K256" t="n">
+        <v>0</v>
+      </c>
+      <c r="L256" t="n">
+        <v>0</v>
+      </c>
+      <c r="M256" t="n">
+        <v>0</v>
+      </c>
+      <c r="N256" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1300100/</t>
         </is>
@@ -10949,7 +14799,22 @@
           <t>1989</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr">
+      <c r="I257" t="n">
+        <v>0</v>
+      </c>
+      <c r="J257" t="n">
+        <v>0</v>
+      </c>
+      <c r="K257" t="n">
+        <v>0</v>
+      </c>
+      <c r="L257" t="n">
+        <v>0</v>
+      </c>
+      <c r="M257" t="n">
+        <v>0</v>
+      </c>
+      <c r="N257" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3098834/</t>
         </is>
@@ -10990,7 +14855,22 @@
           <t>1983-02-13</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr">
+      <c r="I258" t="n">
+        <v>0</v>
+      </c>
+      <c r="J258" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" t="n">
+        <v>0</v>
+      </c>
+      <c r="L258" t="n">
+        <v>0</v>
+      </c>
+      <c r="M258" t="n">
+        <v>1</v>
+      </c>
+      <c r="N258" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1302191/</t>
         </is>
@@ -11031,7 +14911,22 @@
           <t>1962</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr">
+      <c r="I259" t="n">
+        <v>0</v>
+      </c>
+      <c r="J259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K259" t="n">
+        <v>0</v>
+      </c>
+      <c r="L259" t="n">
+        <v>0</v>
+      </c>
+      <c r="M259" t="n">
+        <v>0</v>
+      </c>
+      <c r="N259" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3022872/</t>
         </is>
@@ -11072,7 +14967,22 @@
           <t>1949</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr">
+      <c r="I260" t="n">
+        <v>0</v>
+      </c>
+      <c r="J260" t="n">
+        <v>0</v>
+      </c>
+      <c r="K260" t="n">
+        <v>0</v>
+      </c>
+      <c r="L260" t="n">
+        <v>0</v>
+      </c>
+      <c r="M260" t="n">
+        <v>0</v>
+      </c>
+      <c r="N260" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1494221/</t>
         </is>
@@ -11113,7 +15023,22 @@
           <t>2001</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr">
+      <c r="I261" t="n">
+        <v>0</v>
+      </c>
+      <c r="J261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K261" t="n">
+        <v>0</v>
+      </c>
+      <c r="L261" t="n">
+        <v>0</v>
+      </c>
+      <c r="M261" t="n">
+        <v>0</v>
+      </c>
+      <c r="N261" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3062740/</t>
         </is>
@@ -11154,7 +15079,22 @@
           <t>2016-07-01</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr">
+      <c r="I262" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" t="n">
+        <v>0</v>
+      </c>
+      <c r="L262" t="n">
+        <v>1</v>
+      </c>
+      <c r="M262" t="n">
+        <v>0</v>
+      </c>
+      <c r="N262" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26431412/</t>
         </is>
@@ -11195,7 +15135,22 @@
           <t>1976-10-28</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr">
+      <c r="I263" t="n">
+        <v>0</v>
+      </c>
+      <c r="J263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K263" t="n">
+        <v>0</v>
+      </c>
+      <c r="L263" t="n">
+        <v>0</v>
+      </c>
+      <c r="M263" t="n">
+        <v>0</v>
+      </c>
+      <c r="N263" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1985222/</t>
         </is>
@@ -11236,7 +15191,22 @@
           <t>2013-03-22</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr">
+      <c r="I264" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" t="n">
+        <v>0</v>
+      </c>
+      <c r="M264" t="n">
+        <v>0</v>
+      </c>
+      <c r="N264" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19967789/</t>
         </is>
@@ -11277,7 +15247,22 @@
           <t>1975</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr">
+      <c r="I265" t="n">
+        <v>0</v>
+      </c>
+      <c r="J265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K265" t="n">
+        <v>0</v>
+      </c>
+      <c r="L265" t="n">
+        <v>0</v>
+      </c>
+      <c r="M265" t="n">
+        <v>0</v>
+      </c>
+      <c r="N265" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1483966/</t>
         </is>
@@ -11318,7 +15303,22 @@
           <t>2021-02-12</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr">
+      <c r="I266" t="n">
+        <v>1</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="n">
+        <v>0</v>
+      </c>
+      <c r="L266" t="n">
+        <v>0</v>
+      </c>
+      <c r="M266" t="n">
+        <v>0</v>
+      </c>
+      <c r="N266" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35017085/</t>
         </is>
@@ -11359,7 +15359,22 @@
           <t>1982</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr">
+      <c r="I267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K267" t="n">
+        <v>0</v>
+      </c>
+      <c r="L267" t="n">
+        <v>0</v>
+      </c>
+      <c r="M267" t="n">
+        <v>0</v>
+      </c>
+      <c r="N267" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2147482/</t>
         </is>
@@ -11400,7 +15415,22 @@
           <t>2014-02-14</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr">
+      <c r="I268" t="n">
+        <v>0</v>
+      </c>
+      <c r="J268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K268" t="n">
+        <v>0</v>
+      </c>
+      <c r="L268" t="n">
+        <v>0</v>
+      </c>
+      <c r="M268" t="n">
+        <v>0</v>
+      </c>
+      <c r="N268" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25761527/</t>
         </is>
@@ -11441,7 +15471,22 @@
           <t>2008-02-09</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr">
+      <c r="I269" t="n">
+        <v>1</v>
+      </c>
+      <c r="J269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K269" t="n">
+        <v>0</v>
+      </c>
+      <c r="L269" t="n">
+        <v>0</v>
+      </c>
+      <c r="M269" t="n">
+        <v>0</v>
+      </c>
+      <c r="N269" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2988163/</t>
         </is>
@@ -11482,7 +15527,22 @@
           <t>2014-09-18</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr">
+      <c r="I270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K270" t="n">
+        <v>0</v>
+      </c>
+      <c r="L270" t="n">
+        <v>0</v>
+      </c>
+      <c r="M270" t="n">
+        <v>0</v>
+      </c>
+      <c r="N270" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25731086/</t>
         </is>
@@ -11523,7 +15583,22 @@
           <t>2019-10-18</t>
         </is>
       </c>
-      <c r="I271" t="inlineStr">
+      <c r="I271" t="n">
+        <v>0</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="n">
+        <v>0</v>
+      </c>
+      <c r="L271" t="n">
+        <v>0</v>
+      </c>
+      <c r="M271" t="n">
+        <v>0</v>
+      </c>
+      <c r="N271" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30384234/</t>
         </is>
@@ -11564,7 +15639,22 @@
           <t>1981</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr">
+      <c r="I272" t="n">
+        <v>0</v>
+      </c>
+      <c r="J272" t="n">
+        <v>0</v>
+      </c>
+      <c r="K272" t="n">
+        <v>0</v>
+      </c>
+      <c r="L272" t="n">
+        <v>0</v>
+      </c>
+      <c r="M272" t="n">
+        <v>0</v>
+      </c>
+      <c r="N272" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2305285/</t>
         </is>
@@ -11605,7 +15695,22 @@
           <t>1989-07-30</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr">
+      <c r="I273" t="n">
+        <v>0</v>
+      </c>
+      <c r="J273" t="n">
+        <v>0</v>
+      </c>
+      <c r="K273" t="n">
+        <v>0</v>
+      </c>
+      <c r="L273" t="n">
+        <v>1</v>
+      </c>
+      <c r="M273" t="n">
+        <v>0</v>
+      </c>
+      <c r="N273" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1299179/</t>
         </is>
@@ -11646,7 +15751,22 @@
           <t>2022-07-30</t>
         </is>
       </c>
-      <c r="I274" t="inlineStr">
+      <c r="I274" t="n">
+        <v>0</v>
+      </c>
+      <c r="J274" t="n">
+        <v>0</v>
+      </c>
+      <c r="K274" t="n">
+        <v>0</v>
+      </c>
+      <c r="L274" t="n">
+        <v>1</v>
+      </c>
+      <c r="M274" t="n">
+        <v>0</v>
+      </c>
+      <c r="N274" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35369572/</t>
         </is>
@@ -11687,7 +15807,22 @@
           <t>1977-04-07</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr">
+      <c r="I275" t="n">
+        <v>0</v>
+      </c>
+      <c r="J275" t="n">
+        <v>0</v>
+      </c>
+      <c r="K275" t="n">
+        <v>0</v>
+      </c>
+      <c r="L275" t="n">
+        <v>0</v>
+      </c>
+      <c r="M275" t="n">
+        <v>0</v>
+      </c>
+      <c r="N275" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1305535/</t>
         </is>
@@ -11728,7 +15863,22 @@
           <t>1979</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr">
+      <c r="I276" t="n">
+        <v>0</v>
+      </c>
+      <c r="J276" t="n">
+        <v>0</v>
+      </c>
+      <c r="K276" t="n">
+        <v>0</v>
+      </c>
+      <c r="L276" t="n">
+        <v>0</v>
+      </c>
+      <c r="M276" t="n">
+        <v>0</v>
+      </c>
+      <c r="N276" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6010023/</t>
         </is>
@@ -11769,7 +15919,22 @@
           <t>2018-05-04</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr">
+      <c r="I277" t="n">
+        <v>0</v>
+      </c>
+      <c r="J277" t="n">
+        <v>0</v>
+      </c>
+      <c r="K277" t="n">
+        <v>0</v>
+      </c>
+      <c r="L277" t="n">
+        <v>0</v>
+      </c>
+      <c r="M277" t="n">
+        <v>0</v>
+      </c>
+      <c r="N277" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30194414/</t>
         </is>
@@ -11810,7 +15975,22 @@
           <t>1976-08-14</t>
         </is>
       </c>
-      <c r="I278" t="inlineStr">
+      <c r="I278" t="n">
+        <v>0</v>
+      </c>
+      <c r="J278" t="n">
+        <v>0</v>
+      </c>
+      <c r="K278" t="n">
+        <v>0</v>
+      </c>
+      <c r="L278" t="n">
+        <v>1</v>
+      </c>
+      <c r="M278" t="n">
+        <v>0</v>
+      </c>
+      <c r="N278" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1985229/</t>
         </is>
@@ -11847,7 +16027,22 @@
           <t>2011-08-01</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr">
+      <c r="I279" t="n">
+        <v>0</v>
+      </c>
+      <c r="J279" t="n">
+        <v>0</v>
+      </c>
+      <c r="K279" t="n">
+        <v>0</v>
+      </c>
+      <c r="L279" t="n">
+        <v>1</v>
+      </c>
+      <c r="M279" t="n">
+        <v>0</v>
+      </c>
+      <c r="N279" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6757721/</t>
         </is>
@@ -11888,7 +16083,22 @@
           <t>2009-09-30</t>
         </is>
       </c>
-      <c r="I280" t="inlineStr">
+      <c r="I280" t="n">
+        <v>0</v>
+      </c>
+      <c r="J280" t="n">
+        <v>1</v>
+      </c>
+      <c r="K280" t="n">
+        <v>0</v>
+      </c>
+      <c r="L280" t="n">
+        <v>0</v>
+      </c>
+      <c r="M280" t="n">
+        <v>0</v>
+      </c>
+      <c r="N280" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4073876/</t>
         </is>
@@ -11929,7 +16139,22 @@
           <t>2021-10-02</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr">
+      <c r="I281" t="n">
+        <v>0</v>
+      </c>
+      <c r="J281" t="n">
+        <v>1</v>
+      </c>
+      <c r="K281" t="n">
+        <v>0</v>
+      </c>
+      <c r="L281" t="n">
+        <v>0</v>
+      </c>
+      <c r="M281" t="n">
+        <v>0</v>
+      </c>
+      <c r="N281" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35309666/</t>
         </is>
@@ -11970,7 +16195,22 @@
           <t>2020-04-02</t>
         </is>
       </c>
-      <c r="I282" t="inlineStr">
+      <c r="I282" t="n">
+        <v>0</v>
+      </c>
+      <c r="J282" t="n">
+        <v>0</v>
+      </c>
+      <c r="K282" t="n">
+        <v>0</v>
+      </c>
+      <c r="L282" t="n">
+        <v>0</v>
+      </c>
+      <c r="M282" t="n">
+        <v>0</v>
+      </c>
+      <c r="N282" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34969164/</t>
         </is>
@@ -12011,7 +16251,22 @@
           <t>2005-04-11</t>
         </is>
       </c>
-      <c r="I283" t="inlineStr">
+      <c r="I283" t="n">
+        <v>0</v>
+      </c>
+      <c r="J283" t="n">
+        <v>0</v>
+      </c>
+      <c r="K283" t="n">
+        <v>0</v>
+      </c>
+      <c r="L283" t="n">
+        <v>0</v>
+      </c>
+      <c r="M283" t="n">
+        <v>0</v>
+      </c>
+      <c r="N283" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2330215/</t>
         </is>
@@ -12052,7 +16307,22 @@
           <t>2007</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr">
+      <c r="I284" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" t="n">
+        <v>0</v>
+      </c>
+      <c r="K284" t="n">
+        <v>0</v>
+      </c>
+      <c r="L284" t="n">
+        <v>0</v>
+      </c>
+      <c r="M284" t="n">
+        <v>0</v>
+      </c>
+      <c r="N284" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3271513/</t>
         </is>
@@ -12093,7 +16363,22 @@
           <t>2013-10-18</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr">
+      <c r="I285" t="n">
+        <v>0</v>
+      </c>
+      <c r="J285" t="n">
+        <v>0</v>
+      </c>
+      <c r="K285" t="n">
+        <v>0</v>
+      </c>
+      <c r="L285" t="n">
+        <v>0</v>
+      </c>
+      <c r="M285" t="n">
+        <v>0</v>
+      </c>
+      <c r="N285" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24530628/</t>
         </is>
@@ -12134,7 +16419,22 @@
           <t>2020-03-05</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr">
+      <c r="I286" t="n">
+        <v>0</v>
+      </c>
+      <c r="J286" t="n">
+        <v>0</v>
+      </c>
+      <c r="K286" t="n">
+        <v>0</v>
+      </c>
+      <c r="L286" t="n">
+        <v>0</v>
+      </c>
+      <c r="M286" t="n">
+        <v>0</v>
+      </c>
+      <c r="N286" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30413195/</t>
         </is>
@@ -12175,7 +16475,22 @@
           <t>2020-12-07</t>
         </is>
       </c>
-      <c r="I287" t="inlineStr">
+      <c r="I287" t="n">
+        <v>0</v>
+      </c>
+      <c r="J287" t="n">
+        <v>0</v>
+      </c>
+      <c r="K287" t="n">
+        <v>0</v>
+      </c>
+      <c r="L287" t="n">
+        <v>0</v>
+      </c>
+      <c r="M287" t="n">
+        <v>0</v>
+      </c>
+      <c r="N287" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/33441927/</t>
         </is>
@@ -12216,7 +16531,22 @@
           <t>2019-12-27</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr">
+      <c r="I288" t="n">
+        <v>0</v>
+      </c>
+      <c r="J288" t="n">
+        <v>0</v>
+      </c>
+      <c r="K288" t="n">
+        <v>0</v>
+      </c>
+      <c r="L288" t="n">
+        <v>0</v>
+      </c>
+      <c r="M288" t="n">
+        <v>0</v>
+      </c>
+      <c r="N288" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30454698/</t>
         </is>
@@ -12257,7 +16587,22 @@
           <t>2016-01-01</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr">
+      <c r="I289" t="n">
+        <v>0</v>
+      </c>
+      <c r="J289" t="n">
+        <v>0</v>
+      </c>
+      <c r="K289" t="n">
+        <v>0</v>
+      </c>
+      <c r="L289" t="n">
+        <v>0</v>
+      </c>
+      <c r="M289" t="n">
+        <v>0</v>
+      </c>
+      <c r="N289" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26671674/</t>
         </is>
@@ -12298,7 +16643,22 @@
           <t>2022-04-08</t>
         </is>
       </c>
-      <c r="I290" t="inlineStr">
+      <c r="I290" t="n">
+        <v>0</v>
+      </c>
+      <c r="J290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K290" t="n">
+        <v>0</v>
+      </c>
+      <c r="L290" t="n">
+        <v>0</v>
+      </c>
+      <c r="M290" t="n">
+        <v>0</v>
+      </c>
+      <c r="N290" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35814905/</t>
         </is>
@@ -12339,7 +16699,22 @@
           <t>2013-01-25</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr">
+      <c r="I291" t="n">
+        <v>0</v>
+      </c>
+      <c r="J291" t="n">
+        <v>0</v>
+      </c>
+      <c r="K291" t="n">
+        <v>0</v>
+      </c>
+      <c r="L291" t="n">
+        <v>0</v>
+      </c>
+      <c r="M291" t="n">
+        <v>0</v>
+      </c>
+      <c r="N291" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19977815/</t>
         </is>
@@ -12380,7 +16755,22 @@
           <t>2017-11-03</t>
         </is>
       </c>
-      <c r="I292" t="inlineStr">
+      <c r="I292" t="n">
+        <v>0</v>
+      </c>
+      <c r="J292" t="n">
+        <v>0</v>
+      </c>
+      <c r="K292" t="n">
+        <v>0</v>
+      </c>
+      <c r="L292" t="n">
+        <v>0</v>
+      </c>
+      <c r="M292" t="n">
+        <v>0</v>
+      </c>
+      <c r="N292" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26316956/</t>
         </is>
@@ -12421,7 +16811,22 @@
           <t>2020-02-09</t>
         </is>
       </c>
-      <c r="I293" t="inlineStr">
+      <c r="I293" t="n">
+        <v>0</v>
+      </c>
+      <c r="J293" t="n">
+        <v>0</v>
+      </c>
+      <c r="K293" t="n">
+        <v>0</v>
+      </c>
+      <c r="L293" t="n">
+        <v>0</v>
+      </c>
+      <c r="M293" t="n">
+        <v>1</v>
+      </c>
+      <c r="N293" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34961646/</t>
         </is>
@@ -12462,7 +16867,22 @@
           <t>2022-03-03</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr">
+      <c r="I294" t="n">
+        <v>0</v>
+      </c>
+      <c r="J294" t="n">
+        <v>0</v>
+      </c>
+      <c r="K294" t="n">
+        <v>0</v>
+      </c>
+      <c r="L294" t="n">
+        <v>0</v>
+      </c>
+      <c r="M294" t="n">
+        <v>0</v>
+      </c>
+      <c r="N294" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35786349/</t>
         </is>
@@ -12503,7 +16923,22 @@
           <t>2020-09-09</t>
         </is>
       </c>
-      <c r="I295" t="inlineStr">
+      <c r="I295" t="n">
+        <v>0</v>
+      </c>
+      <c r="J295" t="n">
+        <v>0</v>
+      </c>
+      <c r="K295" t="n">
+        <v>0</v>
+      </c>
+      <c r="L295" t="n">
+        <v>0</v>
+      </c>
+      <c r="M295" t="n">
+        <v>0</v>
+      </c>
+      <c r="N295" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34800544/</t>
         </is>
@@ -12544,7 +16979,22 @@
           <t>2011-06-10</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr">
+      <c r="I296" t="n">
+        <v>0</v>
+      </c>
+      <c r="J296" t="n">
+        <v>0</v>
+      </c>
+      <c r="K296" t="n">
+        <v>0</v>
+      </c>
+      <c r="L296" t="n">
+        <v>0</v>
+      </c>
+      <c r="M296" t="n">
+        <v>0</v>
+      </c>
+      <c r="N296" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5326560/</t>
         </is>
@@ -12585,7 +17035,22 @@
           <t>1989</t>
         </is>
       </c>
-      <c r="I297" t="inlineStr">
+      <c r="I297" t="n">
+        <v>0</v>
+      </c>
+      <c r="J297" t="n">
+        <v>0</v>
+      </c>
+      <c r="K297" t="n">
+        <v>0</v>
+      </c>
+      <c r="L297" t="n">
+        <v>0</v>
+      </c>
+      <c r="M297" t="n">
+        <v>0</v>
+      </c>
+      <c r="N297" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3993263/</t>
         </is>
@@ -12626,7 +17091,22 @@
           <t>2020-05-07</t>
         </is>
       </c>
-      <c r="I298" t="inlineStr">
+      <c r="I298" t="n">
+        <v>0</v>
+      </c>
+      <c r="J298" t="n">
+        <v>0</v>
+      </c>
+      <c r="K298" t="n">
+        <v>0</v>
+      </c>
+      <c r="L298" t="n">
+        <v>0</v>
+      </c>
+      <c r="M298" t="n">
+        <v>0</v>
+      </c>
+      <c r="N298" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34833858/</t>
         </is>
@@ -12667,7 +17147,22 @@
           <t>2023-07-15</t>
         </is>
       </c>
-      <c r="I299" t="inlineStr">
+      <c r="I299" t="n">
+        <v>0</v>
+      </c>
+      <c r="J299" t="n">
+        <v>0</v>
+      </c>
+      <c r="K299" t="n">
+        <v>0</v>
+      </c>
+      <c r="L299" t="n">
+        <v>1</v>
+      </c>
+      <c r="M299" t="n">
+        <v>0</v>
+      </c>
+      <c r="N299" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36445573/</t>
         </is>
@@ -12708,7 +17203,22 @@
           <t>2019-10-24</t>
         </is>
       </c>
-      <c r="I300" t="inlineStr">
+      <c r="I300" t="n">
+        <v>0</v>
+      </c>
+      <c r="J300" t="n">
+        <v>0</v>
+      </c>
+      <c r="K300" t="n">
+        <v>0</v>
+      </c>
+      <c r="L300" t="n">
+        <v>0</v>
+      </c>
+      <c r="M300" t="n">
+        <v>0</v>
+      </c>
+      <c r="N300" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34845733/</t>
         </is>
@@ -12749,7 +17259,22 @@
           <t>2020-01-05</t>
         </is>
       </c>
-      <c r="I301" t="inlineStr">
+      <c r="I301" t="n">
+        <v>0</v>
+      </c>
+      <c r="J301" t="n">
+        <v>0</v>
+      </c>
+      <c r="K301" t="n">
+        <v>0</v>
+      </c>
+      <c r="L301" t="n">
+        <v>0</v>
+      </c>
+      <c r="M301" t="n">
+        <v>1</v>
+      </c>
+      <c r="N301" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30468900/</t>
         </is>
@@ -12790,7 +17315,22 @@
           <t>2019-06-21</t>
         </is>
       </c>
-      <c r="I302" t="inlineStr">
+      <c r="I302" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" t="n">
+        <v>0</v>
+      </c>
+      <c r="L302" t="n">
+        <v>0</v>
+      </c>
+      <c r="M302" t="n">
+        <v>0</v>
+      </c>
+      <c r="N302" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30463515/</t>
         </is>
@@ -12831,7 +17371,22 @@
           <t>2019-10-16</t>
         </is>
       </c>
-      <c r="I303" t="inlineStr">
+      <c r="I303" t="n">
+        <v>0</v>
+      </c>
+      <c r="J303" t="n">
+        <v>0</v>
+      </c>
+      <c r="K303" t="n">
+        <v>0</v>
+      </c>
+      <c r="L303" t="n">
+        <v>0</v>
+      </c>
+      <c r="M303" t="n">
+        <v>0</v>
+      </c>
+      <c r="N303" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30345265/</t>
         </is>
@@ -12872,7 +17427,22 @@
           <t>2020-04-17</t>
         </is>
       </c>
-      <c r="I304" t="inlineStr">
+      <c r="I304" t="n">
+        <v>0</v>
+      </c>
+      <c r="J304" t="n">
+        <v>0</v>
+      </c>
+      <c r="K304" t="n">
+        <v>0</v>
+      </c>
+      <c r="L304" t="n">
+        <v>0</v>
+      </c>
+      <c r="M304" t="n">
+        <v>0</v>
+      </c>
+      <c r="N304" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34482017/</t>
         </is>
@@ -12913,7 +17483,22 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="I305" t="inlineStr">
+      <c r="I305" t="n">
+        <v>0</v>
+      </c>
+      <c r="J305" t="n">
+        <v>0</v>
+      </c>
+      <c r="K305" t="n">
+        <v>0</v>
+      </c>
+      <c r="L305" t="n">
+        <v>1</v>
+      </c>
+      <c r="M305" t="n">
+        <v>0</v>
+      </c>
+      <c r="N305" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36912992/</t>
         </is>
@@ -12954,7 +17539,22 @@
           <t>2018-08-01</t>
         </is>
       </c>
-      <c r="I306" t="inlineStr">
+      <c r="I306" t="n">
+        <v>0</v>
+      </c>
+      <c r="J306" t="n">
+        <v>0</v>
+      </c>
+      <c r="K306" t="n">
+        <v>0</v>
+      </c>
+      <c r="L306" t="n">
+        <v>1</v>
+      </c>
+      <c r="M306" t="n">
+        <v>0</v>
+      </c>
+      <c r="N306" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27180974/</t>
         </is>
@@ -12995,7 +17595,22 @@
           <t>2021-02-11</t>
         </is>
       </c>
-      <c r="I307" t="inlineStr">
+      <c r="I307" t="n">
+        <v>1</v>
+      </c>
+      <c r="J307" t="n">
+        <v>0</v>
+      </c>
+      <c r="K307" t="n">
+        <v>0</v>
+      </c>
+      <c r="L307" t="n">
+        <v>0</v>
+      </c>
+      <c r="M307" t="n">
+        <v>0</v>
+      </c>
+      <c r="N307" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35354409/</t>
         </is>
@@ -13036,7 +17651,22 @@
           <t>2017-06-16</t>
         </is>
       </c>
-      <c r="I308" t="inlineStr">
+      <c r="I308" t="n">
+        <v>0</v>
+      </c>
+      <c r="J308" t="n">
+        <v>0</v>
+      </c>
+      <c r="K308" t="n">
+        <v>0</v>
+      </c>
+      <c r="L308" t="n">
+        <v>0</v>
+      </c>
+      <c r="M308" t="n">
+        <v>0</v>
+      </c>
+      <c r="N308" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26266924/</t>
         </is>
@@ -13077,7 +17707,22 @@
           <t>2011-04-12</t>
         </is>
       </c>
-      <c r="I309" t="inlineStr">
+      <c r="I309" t="n">
+        <v>0</v>
+      </c>
+      <c r="J309" t="n">
+        <v>0</v>
+      </c>
+      <c r="K309" t="n">
+        <v>0</v>
+      </c>
+      <c r="L309" t="n">
+        <v>0</v>
+      </c>
+      <c r="M309" t="n">
+        <v>0</v>
+      </c>
+      <c r="N309" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4707585/</t>
         </is>
@@ -13118,7 +17763,22 @@
           <t>2015-09-24</t>
         </is>
       </c>
-      <c r="I310" t="inlineStr">
+      <c r="I310" t="n">
+        <v>0</v>
+      </c>
+      <c r="J310" t="n">
+        <v>0</v>
+      </c>
+      <c r="K310" t="n">
+        <v>0</v>
+      </c>
+      <c r="L310" t="n">
+        <v>0</v>
+      </c>
+      <c r="M310" t="n">
+        <v>0</v>
+      </c>
+      <c r="N310" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26378587/</t>
         </is>
@@ -13159,7 +17819,22 @@
           <t>2020-05-29</t>
         </is>
       </c>
-      <c r="I311" t="inlineStr">
+      <c r="I311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J311" t="n">
+        <v>0</v>
+      </c>
+      <c r="K311" t="n">
+        <v>0</v>
+      </c>
+      <c r="L311" t="n">
+        <v>0</v>
+      </c>
+      <c r="M311" t="n">
+        <v>0</v>
+      </c>
+      <c r="N311" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34943661/</t>
         </is>
@@ -13200,7 +17875,22 @@
           <t>2015-09-01</t>
         </is>
       </c>
-      <c r="I312" t="inlineStr">
+      <c r="I312" t="n">
+        <v>0</v>
+      </c>
+      <c r="J312" t="n">
+        <v>0</v>
+      </c>
+      <c r="K312" t="n">
+        <v>0</v>
+      </c>
+      <c r="L312" t="n">
+        <v>0</v>
+      </c>
+      <c r="M312" t="n">
+        <v>0</v>
+      </c>
+      <c r="N312" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26578123/</t>
         </is>
@@ -13241,7 +17931,22 @@
           <t>2013-04-28</t>
         </is>
       </c>
-      <c r="I313" t="inlineStr">
+      <c r="I313" t="n">
+        <v>0</v>
+      </c>
+      <c r="J313" t="n">
+        <v>0</v>
+      </c>
+      <c r="K313" t="n">
+        <v>1</v>
+      </c>
+      <c r="L313" t="n">
+        <v>0</v>
+      </c>
+      <c r="M313" t="n">
+        <v>0</v>
+      </c>
+      <c r="N313" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19977818/</t>
         </is>
@@ -13282,7 +17987,22 @@
           <t>2012-09-21</t>
         </is>
       </c>
-      <c r="I314" t="inlineStr">
+      <c r="I314" t="n">
+        <v>0</v>
+      </c>
+      <c r="J314" t="n">
+        <v>0</v>
+      </c>
+      <c r="K314" t="n">
+        <v>0</v>
+      </c>
+      <c r="L314" t="n">
+        <v>0</v>
+      </c>
+      <c r="M314" t="n">
+        <v>0</v>
+      </c>
+      <c r="N314" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10527199/</t>
         </is>
@@ -13323,7 +18043,22 @@
           <t>2023-07-08</t>
         </is>
       </c>
-      <c r="I315" t="inlineStr">
+      <c r="I315" t="n">
+        <v>0</v>
+      </c>
+      <c r="J315" t="n">
+        <v>0</v>
+      </c>
+      <c r="K315" t="n">
+        <v>0</v>
+      </c>
+      <c r="L315" t="n">
+        <v>1</v>
+      </c>
+      <c r="M315" t="n">
+        <v>0</v>
+      </c>
+      <c r="N315" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36464717/</t>
         </is>
@@ -13364,7 +18099,22 @@
           <t>2020-02-01</t>
         </is>
       </c>
-      <c r="I316" t="inlineStr">
+      <c r="I316" t="n">
+        <v>1</v>
+      </c>
+      <c r="J316" t="n">
+        <v>0</v>
+      </c>
+      <c r="K316" t="n">
+        <v>0</v>
+      </c>
+      <c r="L316" t="n">
+        <v>0</v>
+      </c>
+      <c r="M316" t="n">
+        <v>0</v>
+      </c>
+      <c r="N316" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34833914/</t>
         </is>
@@ -13405,7 +18155,22 @@
           <t>2012-10-20</t>
         </is>
       </c>
-      <c r="I317" t="inlineStr">
+      <c r="I317" t="n">
+        <v>0</v>
+      </c>
+      <c r="J317" t="n">
+        <v>0</v>
+      </c>
+      <c r="K317" t="n">
+        <v>0</v>
+      </c>
+      <c r="L317" t="n">
+        <v>0</v>
+      </c>
+      <c r="M317" t="n">
+        <v>1</v>
+      </c>
+      <c r="N317" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11636794/</t>
         </is>
@@ -13446,7 +18211,22 @@
           <t>2012-04-19</t>
         </is>
       </c>
-      <c r="I318" t="inlineStr">
+      <c r="I318" t="n">
+        <v>0</v>
+      </c>
+      <c r="J318" t="n">
+        <v>0</v>
+      </c>
+      <c r="K318" t="n">
+        <v>0</v>
+      </c>
+      <c r="L318" t="n">
+        <v>0</v>
+      </c>
+      <c r="M318" t="n">
+        <v>0</v>
+      </c>
+      <c r="N318" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6845675/</t>
         </is>
@@ -13487,7 +18267,22 @@
           <t>2014-05-30</t>
         </is>
       </c>
-      <c r="I319" t="inlineStr">
+      <c r="I319" t="n">
+        <v>0</v>
+      </c>
+      <c r="J319" t="n">
+        <v>0</v>
+      </c>
+      <c r="K319" t="n">
+        <v>0</v>
+      </c>
+      <c r="L319" t="n">
+        <v>0</v>
+      </c>
+      <c r="M319" t="n">
+        <v>0</v>
+      </c>
+      <c r="N319" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25869685/</t>
         </is>
@@ -13528,7 +18323,22 @@
           <t>2018-11-23</t>
         </is>
       </c>
-      <c r="I320" t="inlineStr">
+      <c r="I320" t="n">
+        <v>0</v>
+      </c>
+      <c r="J320" t="n">
+        <v>0</v>
+      </c>
+      <c r="K320" t="n">
+        <v>0</v>
+      </c>
+      <c r="L320" t="n">
+        <v>0</v>
+      </c>
+      <c r="M320" t="n">
+        <v>0</v>
+      </c>
+      <c r="N320" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27102739/</t>
         </is>
@@ -13569,7 +18379,22 @@
           <t>2011-11-18</t>
         </is>
       </c>
-      <c r="I321" t="inlineStr">
+      <c r="I321" t="n">
+        <v>0</v>
+      </c>
+      <c r="J321" t="n">
+        <v>0</v>
+      </c>
+      <c r="K321" t="n">
+        <v>0</v>
+      </c>
+      <c r="L321" t="n">
+        <v>0</v>
+      </c>
+      <c r="M321" t="n">
+        <v>0</v>
+      </c>
+      <c r="N321" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4824982/</t>
         </is>
@@ -13610,7 +18435,22 @@
           <t>2018-03-03</t>
         </is>
       </c>
-      <c r="I322" t="inlineStr">
+      <c r="I322" t="n">
+        <v>0</v>
+      </c>
+      <c r="J322" t="n">
+        <v>0</v>
+      </c>
+      <c r="K322" t="n">
+        <v>0</v>
+      </c>
+      <c r="L322" t="n">
+        <v>0</v>
+      </c>
+      <c r="M322" t="n">
+        <v>1</v>
+      </c>
+      <c r="N322" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30155226/</t>
         </is>
@@ -13651,7 +18491,22 @@
           <t>2013-03-01</t>
         </is>
       </c>
-      <c r="I323" t="inlineStr">
+      <c r="I323" t="n">
+        <v>0</v>
+      </c>
+      <c r="J323" t="n">
+        <v>0</v>
+      </c>
+      <c r="K323" t="n">
+        <v>0</v>
+      </c>
+      <c r="L323" t="n">
+        <v>0</v>
+      </c>
+      <c r="M323" t="n">
+        <v>0</v>
+      </c>
+      <c r="N323" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19944520/</t>
         </is>
@@ -13692,7 +18547,22 @@
           <t>2016-07-01</t>
         </is>
       </c>
-      <c r="I324" t="inlineStr">
+      <c r="I324" t="n">
+        <v>0</v>
+      </c>
+      <c r="J324" t="n">
+        <v>0</v>
+      </c>
+      <c r="K324" t="n">
+        <v>0</v>
+      </c>
+      <c r="L324" t="n">
+        <v>1</v>
+      </c>
+      <c r="M324" t="n">
+        <v>0</v>
+      </c>
+      <c r="N324" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26656564/</t>
         </is>
@@ -13733,7 +18603,22 @@
           <t>2013-05-24</t>
         </is>
       </c>
-      <c r="I325" t="inlineStr">
+      <c r="I325" t="n">
+        <v>0</v>
+      </c>
+      <c r="J325" t="n">
+        <v>0</v>
+      </c>
+      <c r="K325" t="n">
+        <v>0</v>
+      </c>
+      <c r="L325" t="n">
+        <v>0</v>
+      </c>
+      <c r="M325" t="n">
+        <v>0</v>
+      </c>
+      <c r="N325" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/21323597/</t>
         </is>
@@ -13774,7 +18659,22 @@
           <t>2017-09-22</t>
         </is>
       </c>
-      <c r="I326" t="inlineStr">
+      <c r="I326" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" t="n">
+        <v>0</v>
+      </c>
+      <c r="K326" t="n">
+        <v>0</v>
+      </c>
+      <c r="L326" t="n">
+        <v>0</v>
+      </c>
+      <c r="M326" t="n">
+        <v>0</v>
+      </c>
+      <c r="N326" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27066362/</t>
         </is>
@@ -13815,7 +18715,22 @@
           <t>2018-10-26</t>
         </is>
       </c>
-      <c r="I327" t="inlineStr">
+      <c r="I327" t="n">
+        <v>0</v>
+      </c>
+      <c r="J327" t="n">
+        <v>0</v>
+      </c>
+      <c r="K327" t="n">
+        <v>0</v>
+      </c>
+      <c r="L327" t="n">
+        <v>0</v>
+      </c>
+      <c r="M327" t="n">
+        <v>0</v>
+      </c>
+      <c r="N327" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26331700/</t>
         </is>
@@ -13856,7 +18771,22 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="I328" t="inlineStr">
+      <c r="I328" t="n">
+        <v>0</v>
+      </c>
+      <c r="J328" t="n">
+        <v>0</v>
+      </c>
+      <c r="K328" t="n">
+        <v>0</v>
+      </c>
+      <c r="L328" t="n">
+        <v>1</v>
+      </c>
+      <c r="M328" t="n">
+        <v>0</v>
+      </c>
+      <c r="N328" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26581837/</t>
         </is>
@@ -13897,7 +18827,22 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="I329" t="inlineStr">
+      <c r="I329" t="n">
+        <v>0</v>
+      </c>
+      <c r="J329" t="n">
+        <v>0</v>
+      </c>
+      <c r="K329" t="n">
+        <v>0</v>
+      </c>
+      <c r="L329" t="n">
+        <v>0</v>
+      </c>
+      <c r="M329" t="n">
+        <v>0</v>
+      </c>
+      <c r="N329" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2355418/</t>
         </is>
